--- a/SS_levee_input.xlsx
+++ b/SS_levee_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\Task_FY25_NCMP_Part_1\Chicago_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8747BA51-0057-481A-8FB4-AB7804BB6014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55B2BF3-7798-490B-842F-57974A9A24EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{E6B7D8F3-466A-4168-A43B-4ED2ECFB7BAF}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="17145" xr2:uid="{E6B7D8F3-466A-4168-A43B-4ED2ECFB7BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Levee" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="163">
   <si>
     <t>NA</t>
   </si>
@@ -519,6 +519,12 @@
   </si>
   <si>
     <t>StormSim Project General Inputs</t>
+  </si>
+  <si>
+    <t>compute_wave_transmission</t>
+  </si>
+  <si>
+    <t>Compute wave transmission (eurotop)</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1285,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C278EE8-766D-4C8F-8E2C-2C850EF9EBE7}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
@@ -2336,55 +2342,69 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B56" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>3</v>
-      </c>
       <c r="C56" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D57" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B58" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
+      <c r="C58" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-    </row>
-    <row r="61" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="62" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>

--- a/SS_levee_input.xlsx
+++ b/SS_levee_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_StormSim_Task\StormSim-Library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F55B2BF3-7798-490B-842F-57974A9A24EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A801A25B-117A-42F4-B15E-4FF434AF2DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="28800" windowHeight="17145" xr2:uid="{E6B7D8F3-466A-4168-A43B-4ED2ECFB7BAF}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="23955" windowHeight="20985" xr2:uid="{E6B7D8F3-466A-4168-A43B-4ED2ECFB7BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Levee" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="130">
   <si>
     <t>NA</t>
   </si>
@@ -113,30 +113,6 @@
     <t>[m]</t>
   </si>
   <si>
-    <t>Berm Elevation (Negative Below Datum Zero)</t>
-  </si>
-  <si>
-    <t>berm_elevation</t>
-  </si>
-  <si>
-    <t>Berm Width</t>
-  </si>
-  <si>
-    <t>berm_width</t>
-  </si>
-  <si>
-    <t>Wall Seaward Slope (Same Slope Is Assumed For Landward Slope)</t>
-  </si>
-  <si>
-    <t>berm_slope</t>
-  </si>
-  <si>
-    <t>Add berm in front of structure seaward side (0- No Berm/ 1- Add Berm)</t>
-  </si>
-  <si>
-    <t>add_berm</t>
-  </si>
-  <si>
     <t>Mound Landward Slope (cota)</t>
   </si>
   <si>
@@ -224,33 +200,9 @@
     <t>pros_compute_forcing_HC</t>
   </si>
   <si>
-    <t>Probability Masses (CHS -&gt; Probability_Masses folder relative path, Custom Modeling -&gt; .mat filename with relative path)</t>
-  </si>
-  <si>
-    <t>prob_mass_source</t>
-  </si>
-  <si>
-    <t>Chicago_files</t>
-  </si>
-  <si>
-    <t>CHS Region Grid File (Relative Path)</t>
-  </si>
-  <si>
-    <t>chs_grid_file_source</t>
-  </si>
-  <si>
     <t>StormSim: Probabilistic Run-up, Overtopping &amp; Stone Sizing (PROS)</t>
   </si>
   <si>
-    <t>Chicago_files\CHS-GLMH_ADCIRC_BiasUncertainty_perVG_rta.mat</t>
-  </si>
-  <si>
-    <t>CHS Region Bias File (Relative Path)</t>
-  </si>
-  <si>
-    <t>chs_ssl_bias_and_uncertainty_file</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
@@ -371,42 +323,18 @@
     <t>apply_depth_limitation</t>
   </si>
   <si>
-    <t>Runup Uncertainty</t>
-  </si>
-  <si>
-    <t>r2p_u</t>
-  </si>
-  <si>
     <t>Apply random tide to storm SWL (0 - Off / 1 - On)</t>
   </si>
   <si>
     <t>apply_random_tides</t>
   </si>
   <si>
-    <t>[m^3/s/m]</t>
-  </si>
-  <si>
-    <t>Overtopping Uncertainty</t>
-  </si>
-  <si>
-    <t>q_u</t>
-  </si>
-  <si>
     <t>Sea level rise applied as vertical offset to SWL.</t>
   </si>
   <si>
     <t>swl_slr</t>
   </si>
   <si>
-    <t>[N/m^2]</t>
-  </si>
-  <si>
-    <t>Surface Pressure (p1) Uncertainty' (Floodwalls Only)</t>
-  </si>
-  <si>
-    <t>p1_u</t>
-  </si>
-  <si>
     <t>XC</t>
   </si>
   <si>
@@ -416,12 +344,6 @@
     <t>storm_sampling</t>
   </si>
   <si>
-    <t>Dn50 Uncertainty</t>
-  </si>
-  <si>
-    <t>dn50_u</t>
-  </si>
-  <si>
     <t>Structure type  (Levee - 1, Floodwalls - 2, Rubblemound - 3)</t>
   </si>
   <si>
@@ -434,9 +356,6 @@
     <t>workflow</t>
   </si>
   <si>
-    <t>StormSim Project Structure Response Uncertainty</t>
-  </si>
-  <si>
     <t>[84 90]</t>
   </si>
   <si>
@@ -455,12 +374,6 @@
     <t>project_datum</t>
   </si>
   <si>
-    <t>Hm0 Proportional Uncertainty, U_r</t>
-  </si>
-  <si>
-    <t>chs_hm0_u_r</t>
-  </si>
-  <si>
     <t>SS_Outputs_7175_T3</t>
   </si>
   <si>
@@ -470,12 +383,6 @@
     <t>outfolder</t>
   </si>
   <si>
-    <t>Hm0 Absolute Uncertainty, U_a</t>
-  </si>
-  <si>
-    <t>chs_hm0_u_a</t>
-  </si>
-  <si>
     <t>Seawall_existing</t>
   </si>
   <si>
@@ -485,12 +392,6 @@
     <t>case_name</t>
   </si>
   <si>
-    <t>SWL Proportional Uncertainty, U_r</t>
-  </si>
-  <si>
-    <t>chs_swl_u_r</t>
-  </si>
-  <si>
     <t>R7175_T3</t>
   </si>
   <si>
@@ -500,12 +401,6 @@
     <t>struc_id</t>
   </si>
   <si>
-    <t>SWL Absolute Uncertainty, U_a</t>
-  </si>
-  <si>
-    <t>chs_swl_u_a</t>
-  </si>
-  <si>
     <t>Chicago Shoreline GRR</t>
   </si>
   <si>
@@ -515,9 +410,6 @@
     <t>project_name</t>
   </si>
   <si>
-    <t xml:space="preserve">StormSim Project Forcing Uncertainty </t>
-  </si>
-  <si>
     <t>StormSim Project General Inputs</t>
   </si>
   <si>
@@ -525,16 +417,22 @@
   </si>
   <si>
     <t>Compute wave transmission (eurotop)</t>
+  </si>
+  <si>
+    <t>chs_dependencies</t>
+  </si>
+  <si>
+    <t>CHS regional dependencies folder</t>
+  </si>
+  <si>
+    <t>..\CHS_Dependencies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,21 +462,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,14 +535,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="14">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -752,7 +636,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -763,7 +647,7 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -772,11 +656,11 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -785,8 +669,12 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -797,34 +685,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -834,11 +694,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -875,6 +734,34 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -882,59 +769,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -944,34 +791,21 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1299,25 +1133,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="F1" s="55" t="s">
-        <v>159</v>
-      </c>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
+      <c r="A1" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="F1" s="45" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>14</v>
@@ -1339,153 +1177,153 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>156</v>
-      </c>
-      <c r="F3" s="53" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="53" t="s">
-        <v>154</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="54">
-        <v>9.3515882748499979E-2</v>
+      <c r="A3" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="41">
+        <v>1000</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="53" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I4" s="54">
-        <v>0.35632805802324996</v>
+        <v>118</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I4" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="G5" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I6" s="23">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
-      <c r="H7" s="52"/>
-      <c r="I7" s="52"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>0</v>
@@ -1493,77 +1331,77 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>13</v>
+      <c r="F9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19">
+        <v>103</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16">
         <v>1</v>
       </c>
-      <c r="F10" s="51" t="s">
-        <v>127</v>
+      <c r="F10" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>126</v>
+        <v>63</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>122</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="2">
-        <v>0.43</v>
+      <c r="I11" s="23">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>24</v>
@@ -1571,25 +1409,17 @@
       <c r="D12" s="2">
         <v>176.45</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I12" s="2">
-        <v>0.78</v>
-      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>0</v>
@@ -1597,25 +1427,19 @@
       <c r="D13" s="2">
         <v>0</v>
       </c>
-      <c r="F13" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="26">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F13" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>0</v>
@@ -1623,17 +1447,25 @@
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>0</v>
@@ -1641,23 +1473,25 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="F15" s="49" t="s">
-        <v>106</v>
-      </c>
-      <c r="G15" s="44"/>
-      <c r="H15" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>0</v>
@@ -1665,25 +1499,25 @@
       <c r="D16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>13</v>
+      <c r="F16" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>0</v>
@@ -1691,25 +1525,25 @@
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="F17" s="48" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="47" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="45">
-        <v>1000</v>
+      <c r="F17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>0</v>
@@ -1718,24 +1552,24 @@
         <v>0</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>96</v>
+        <v>41</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>0</v>
@@ -1743,17 +1577,25 @@
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
+      <c r="F19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>0</v>
@@ -1761,83 +1603,53 @@
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="F20" s="43" t="s">
-        <v>89</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
+      <c r="F20" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="23">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
-        <v>88</v>
+      <c r="A21" s="24" t="s">
+        <v>72</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>13</v>
+      <c r="D21" s="23" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="42"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-      <c r="F22" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="30">
-        <v>0</v>
-      </c>
+      <c r="A22" s="38"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="F23" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
+      <c r="A23" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>14</v>
@@ -1845,571 +1657,371 @@
       <c r="D24" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="30">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="27">
         <v>1</v>
       </c>
-      <c r="F25" s="27" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="H25" s="11" t="s">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="27">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="26"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+    </row>
+    <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+    </row>
+    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="30">
-        <v>2.46</v>
-      </c>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="35"/>
-      <c r="H27" s="35"/>
-      <c r="I27" s="35"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F28" s="7" t="s">
+      <c r="D33" s="19">
+        <v>180.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="16">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="15"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="B40" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="D40" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" s="30">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+    </row>
+    <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+    </row>
+    <row r="45" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="29"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="F32" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="F33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I33" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="G34" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="I34" s="26">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="22">
-        <v>180.1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="19">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="2">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D39" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D40" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="19">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="B43" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-    </row>
-    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-    </row>
-    <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D48" s="10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="9"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-    </row>
-    <row r="50" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>13</v>
+      <c r="C51" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D52" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D53" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-    </row>
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+    </row>
+    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="62" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
-    <protectedRange sqref="I3:I6 I10:I14 I22:I25 I29 I17:I18" name="Range1_1"/>
-    <protectedRange sqref="D47:D48" name="Range1_1_4"/>
+    <protectedRange sqref="I15 I3:I4 I8:I11" name="Range1_1"/>
+    <protectedRange sqref="D41:D42" name="Range1_1_4"/>
     <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
     <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
     <protectedRange sqref="D13" name="Range1_1_2"/>
@@ -2417,20 +2029,15 @@
     <protectedRange sqref="D4" name="Range1_1_8"/>
     <protectedRange sqref="D5" name="Range1_1_7"/>
     <protectedRange sqref="D7" name="Range1_1_5"/>
-    <protectedRange sqref="D25" name="Range1_1_3_3"/>
-    <protectedRange sqref="D31" name="Range1_1_2_1_1"/>
-    <protectedRange sqref="D28" name="Range1_1_5_1_1_1_1"/>
-    <protectedRange sqref="D26" name="Range1_1_5_2"/>
-    <protectedRange sqref="D27" name="Range1_1_6_1"/>
-    <protectedRange sqref="D29" name="Range1_1_5_1_1"/>
-    <protectedRange sqref="D30" name="Range1_1_8_1_1"/>
-    <protectedRange sqref="D35" name="Range1_1_3_1_3"/>
-    <protectedRange sqref="D41" name="Range1_1_3_1_1"/>
-    <protectedRange sqref="D40" name="Range1_1_3_1_2_1"/>
-    <protectedRange sqref="D36" name="Range1_1_3_1_4"/>
-    <protectedRange sqref="D37" name="Range1_1_3_1_5"/>
-    <protectedRange sqref="D38" name="Range1_1_3_1_7"/>
-    <protectedRange sqref="D39" name="Range1_1_3_1_8"/>
+    <protectedRange sqref="D33" name="Range1_1_3_1_3"/>
+    <protectedRange sqref="D34" name="Range1_1_3_1_4"/>
+    <protectedRange sqref="D35" name="Range1_1_3_1_5"/>
+    <protectedRange sqref="D36" name="Range1_1_3_1_7"/>
+    <protectedRange sqref="D37" name="Range1_1_3_1_8"/>
+    <protectedRange sqref="D25" name="Range1_1_3_3_1"/>
+    <protectedRange sqref="D29" name="Range1_1_2_1_1_1"/>
+    <protectedRange sqref="D26:D27" name="Range1_1_5_2_1"/>
+    <protectedRange sqref="D28" name="Range1_1_8_1_1_1"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
